--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>IconId</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -138,6 +141,9 @@
   </si>
   <si>
     <t>敌人名称</t>
+  </si>
+  <si>
+    <t>图标ID</t>
   </si>
   <si>
     <t>描述</t>
@@ -234,14 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -697,148 +696,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1193,35 +1192,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:AE16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="32" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="17" width="16" customWidth="1"/>
-    <col min="18" max="24" width="28" customWidth="1"/>
-    <col min="25" max="25" width="32" customWidth="1"/>
-    <col min="26" max="26" width="22" customWidth="1"/>
-    <col min="27" max="27" width="12" customWidth="1"/>
-    <col min="28" max="28" width="32" customWidth="1"/>
-    <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="30" width="17" customWidth="1"/>
+    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="18" width="16" customWidth="1"/>
+    <col min="19" max="25" width="28" customWidth="1"/>
+    <col min="26" max="26" width="32" customWidth="1"/>
+    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="20" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1256,8 +1255,9 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,276 +1346,321 @@
       <c r="AD2" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE2" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30">
+    <row r="5" ht="15" customHeight="1" spans="1:31">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11001</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1" t="b">
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
         <v>15</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>2301</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>1</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>10</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>2</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>0.3</v>
-      </c>
-      <c r="P5" s="1">
-        <v>10</v>
       </c>
       <c r="Q5" s="1">
         <v>10</v>
       </c>
       <c r="R5" s="1">
+        <v>10</v>
+      </c>
+      <c r="S5" s="1">
         <v>3</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <v>60</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>10</v>
       </c>
-      <c r="U5" s="1">
+      <c r="V5" s="1">
         <v>0.5</v>
       </c>
-      <c r="V5" s="1">
+      <c r="W5" s="1">
         <v>0.3</v>
       </c>
-      <c r="W5" s="1">
+      <c r="X5" s="1">
         <v>1</v>
       </c>
-      <c r="X5" s="1">
+      <c r="Y5" s="1">
         <v>3</v>
       </c>
-      <c r="Y5" s="1">
+      <c r="Z5" s="1">
         <v>6</v>
       </c>
-      <c r="Z5" s="1">
+      <c r="AA5" s="1">
         <v>1</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="AB5" s="1">
         <v>4</v>
       </c>
-      <c r="AB5" s="1">
+      <c r="AC5" s="1">
         <v>20</v>
       </c>
-      <c r="AC5" s="1">
+      <c r="AD5" s="1">
         <v>3</v>
       </c>
-      <c r="AD5" s="1">
+      <c r="AE5" s="1">
         <v>1</v>
       </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -240,7 +240,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,148 +703,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1192,14 +1199,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AE5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
@@ -1211,7 +1219,12 @@
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
     <col min="17" max="18" width="16" customWidth="1"/>
-    <col min="19" max="25" width="28" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="23" width="23" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="28" customWidth="1"/>
     <col min="26" max="26" width="32" customWidth="1"/>
     <col min="27" max="27" width="22" customWidth="1"/>
     <col min="28" max="28" width="12" customWidth="1"/>
@@ -1587,22 +1600,22 @@
         <v>10</v>
       </c>
       <c r="R5" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S5" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="T5" s="1">
         <v>60</v>
       </c>
       <c r="U5" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="W5" s="1">
         <v>0.5</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0.3</v>
       </c>
       <c r="X5" s="1">
         <v>1</v>
@@ -1611,10 +1624,10 @@
         <v>3</v>
       </c>
       <c r="Z5" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AB5" s="1">
         <v>4</v>
@@ -1623,44 +1636,11 @@
         <v>20</v>
       </c>
       <c r="AD5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31">
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:31">
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:31">
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:31">
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:31">
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:31">
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:31">
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:31">
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:31">
-      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -240,14 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,148 +696,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1582,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>2301</v>
+        <v>2601</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -228,6 +228,24 @@
   </si>
   <si>
     <t>测试</t>
+  </si>
+  <si>
+    <t>普通敌人-容易</t>
+  </si>
+  <si>
+    <t>容易难度</t>
+  </si>
+  <si>
+    <t>普通敌人-普通</t>
+  </si>
+  <si>
+    <t>普通难度</t>
+  </si>
+  <si>
+    <t>精英敌人-困难</t>
+  </si>
+  <si>
+    <t>困难难度</t>
   </si>
 </sst>
 </file>
@@ -240,7 +258,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,148 +721,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1192,13 +1217,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
@@ -1593,7 +1618,7 @@
         <v>10</v>
       </c>
       <c r="R5" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S5" s="1">
         <v>1.5</v>
@@ -1614,13 +1639,13 @@
         <v>1</v>
       </c>
       <c r="Y5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AB5" s="1">
         <v>4</v>
@@ -1629,10 +1654,283 @@
         <v>20</v>
       </c>
       <c r="AD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:31">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="AE5" s="1">
-        <v>1</v>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="1">
+        <v>11001</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>8</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>8</v>
+      </c>
+      <c r="R6" s="1">
+        <v>20</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T6" s="1">
+        <v>60</v>
+      </c>
+      <c r="U6" s="1">
+        <v>8</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>25</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:31">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1">
+        <v>11001</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
+        <v>10</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1">
+        <v>15</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T7" s="1">
+        <v>60</v>
+      </c>
+      <c r="U7" s="1">
+        <v>8</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>20</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:31">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="1">
+        <v>11001</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>18</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>12</v>
+      </c>
+      <c r="O8" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>12</v>
+      </c>
+      <c r="R8" s="1">
+        <v>12</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="1">
+        <v>60</v>
+      </c>
+      <c r="U8" s="1">
+        <v>8</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>18</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1218,7 +1218,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -1663,7 +1663,7 @@
         <v>3</v>
       </c>
       <c r="AE5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:31">

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -119,7 +119,7 @@
     <t>CombatDistance</t>
   </si>
   <si>
-    <t>Difficulty</t>
+    <t>EnemyDifficulty</t>
   </si>
   <si>
     <t>int</t>
@@ -264,14 +264,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,148 +720,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>EnemyIconId</t>
+  </si>
+  <si>
     <t>EnemyType</t>
   </si>
   <si>
@@ -149,6 +152,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>敌人头像资源ID</t>
+  </si>
+  <si>
     <t>敌人类型(0=普通,1=精英,2=Boss)</t>
   </si>
   <si>
@@ -224,31 +230,31 @@
     <t>难度系数（1-5）</t>
   </si>
   <si>
-    <t>后羿敌人测试</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>普通敌人-容易</t>
-  </si>
-  <si>
-    <t>容易难度</t>
-  </si>
-  <si>
-    <t>普通敌人-普通</t>
-  </si>
-  <si>
-    <t>普通难度</t>
-  </si>
-  <si>
-    <t>精英敌人-困难</t>
-  </si>
-  <si>
-    <t>困难难度</t>
-  </si>
-  <si>
-    <t>Boss敌人-王者</t>
+    <t>邪灵-普通</t>
+  </si>
+  <si>
+    <t>邪灵-普通难度</t>
+  </si>
+  <si>
+    <t>恶魂-普通</t>
+  </si>
+  <si>
+    <t>恶魂-普通难度</t>
+  </si>
+  <si>
+    <t>邪灵-精英</t>
+  </si>
+  <si>
+    <t>邪灵-精英难度</t>
+  </si>
+  <si>
+    <t>恶魂-精英</t>
+  </si>
+  <si>
+    <t>恶魂-精英难度</t>
+  </si>
+  <si>
+    <t>黑暗杨戬-Boss</t>
   </si>
   <si>
     <t>Boss难度</t>
@@ -264,7 +270,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,148 +733,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1216,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1224,33 +1237,34 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="28" customWidth="1"/>
-    <col min="26" max="26" width="32" customWidth="1"/>
-    <col min="27" max="27" width="22" customWidth="1"/>
-    <col min="28" max="28" width="12" customWidth="1"/>
-    <col min="29" max="29" width="32" customWidth="1"/>
-    <col min="30" max="30" width="20" customWidth="1"/>
-    <col min="31" max="31" width="17" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="17" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="24" width="23" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="26" width="28" customWidth="1"/>
+    <col min="27" max="27" width="32" customWidth="1"/>
+    <col min="28" max="28" width="22" customWidth="1"/>
+    <col min="29" max="29" width="12" customWidth="1"/>
+    <col min="30" max="30" width="32" customWidth="1"/>
+    <col min="31" max="31" width="20" customWidth="1"/>
+    <col min="32" max="32" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1286,8 +1300,9 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,647 +1394,671 @@
       <c r="AE2" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="AF2" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:31">
+    <row r="5" ht="15" customHeight="1" spans="1:32">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1">
         <v>11001</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5" s="1">
+        <v>1601</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>102</v>
+      </c>
+      <c r="M5" s="1">
+        <v>2601</v>
+      </c>
+      <c r="N5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>15</v>
-      </c>
-      <c r="K5" s="1">
-        <v>102</v>
-      </c>
-      <c r="L5" s="1">
-        <v>2601</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>10</v>
-      </c>
       <c r="O5" s="1">
+        <v>8</v>
+      </c>
+      <c r="P5" s="1">
         <v>2</v>
       </c>
-      <c r="P5" s="1">
-        <v>0.3</v>
-      </c>
       <c r="Q5" s="1">
-        <v>10</v>
+        <v>0.35</v>
       </c>
       <c r="R5" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="S5" s="1">
+        <v>12</v>
+      </c>
+      <c r="T5" s="1">
         <v>1.5</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>60</v>
       </c>
-      <c r="U5" s="1">
-        <v>8</v>
-      </c>
       <c r="V5" s="1">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="W5" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="X5" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="Y5" s="1">
         <v>1</v>
       </c>
       <c r="Z5" s="1">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="AB5" s="1">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="AC5" s="1">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AE5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:31">
+    <row r="6" ht="15" customHeight="1" spans="1:32">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="1">
         <v>11001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1602</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="b">
+      <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>101</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>2601</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>10</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="R6" s="1">
+        <v>10</v>
+      </c>
+      <c r="S6" s="1">
+        <v>20</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U6" s="1">
+        <v>70</v>
+      </c>
+      <c r="V6" s="1">
+        <v>10</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="N6" s="1">
+      <c r="Z6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>25</v>
+      </c>
+      <c r="AE6" s="1">
         <v>8</v>
       </c>
-      <c r="O6" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>8</v>
-      </c>
-      <c r="R6" s="1">
-        <v>20</v>
-      </c>
-      <c r="S6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="T6" s="1">
-        <v>60</v>
-      </c>
-      <c r="U6" s="1">
-        <v>8</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="X6" s="1">
+      <c r="AF6" s="1">
         <v>1</v>
       </c>
-      <c r="Y6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>25</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:31">
+    <row r="7" ht="15" customHeight="1" spans="1:32">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" s="1">
         <v>11001</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1601</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1">
+        <v>101</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2601</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3</v>
+      </c>
+      <c r="O7" s="1">
+        <v>12</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="R7" s="1">
+        <v>6</v>
+      </c>
+      <c r="S7" s="1">
+        <v>16</v>
+      </c>
+      <c r="T7" s="1">
+        <v>2</v>
+      </c>
+      <c r="U7" s="1">
         <v>70</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>101</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2601</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>10</v>
-      </c>
-      <c r="O7" s="1">
-        <v>2</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>10</v>
-      </c>
-      <c r="R7" s="1">
-        <v>15</v>
-      </c>
-      <c r="S7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="T7" s="1">
-        <v>60</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="V7" s="1">
         <v>8</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0.3</v>
       </c>
       <c r="W7" s="1">
         <v>0.5</v>
       </c>
       <c r="X7" s="1">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="Y7" s="1">
         <v>1</v>
       </c>
       <c r="Z7" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="1">
         <v>0.2</v>
       </c>
-      <c r="AB7" s="1">
-        <v>4</v>
-      </c>
       <c r="AC7" s="1">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AD7" s="1">
+        <v>22</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF7" s="1">
         <v>3</v>
       </c>
-      <c r="AE7" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:31">
+    <row r="8" ht="15" customHeight="1" spans="1:32">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1">
         <v>11001</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1">
+        <v>1602</v>
+      </c>
+      <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="b">
+      <c r="I8" s="1">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="1">
-        <v>18</v>
-      </c>
       <c r="K8" s="1">
+        <v>20</v>
+      </c>
+      <c r="L8" s="1">
         <v>102</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>2601</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
+        <v>4</v>
+      </c>
+      <c r="O8" s="1">
+        <v>15</v>
+      </c>
+      <c r="P8" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="R8" s="1">
+        <v>8</v>
+      </c>
+      <c r="S8" s="1">
+        <v>25</v>
+      </c>
+      <c r="T8" s="1">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>80</v>
+      </c>
+      <c r="V8" s="1">
+        <v>14</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="Y8" s="1">
         <v>1</v>
       </c>
-      <c r="N8" s="1">
-        <v>12</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>12</v>
-      </c>
-      <c r="R8" s="1">
-        <v>12</v>
-      </c>
-      <c r="S8" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="T8" s="1">
-        <v>60</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="Z8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="AA8" s="1">
         <v>8</v>
       </c>
-      <c r="V8" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="X8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>0.1</v>
-      </c>
       <c r="AB8" s="1">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="AC8" s="1">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AE8" s="1">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>4</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:31">
+    <row r="9" ht="15" customHeight="1" spans="1:32">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E9" s="1">
         <v>11001</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>1603</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="1" t="b">
+      <c r="I9" s="1">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="1">
-        <v>25</v>
-      </c>
       <c r="K9" s="1">
+        <v>30</v>
+      </c>
+      <c r="L9" s="1">
         <v>103</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>2601</v>
       </c>
-      <c r="M9" s="1">
-        <v>2</v>
-      </c>
       <c r="N9" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O9" s="1">
+        <v>20</v>
+      </c>
+      <c r="P9" s="1">
         <v>3</v>
       </c>
-      <c r="P9" s="1">
-        <v>0.1</v>
-      </c>
       <c r="Q9" s="1">
-        <v>15</v>
+        <v>0.05</v>
       </c>
       <c r="R9" s="1">
+        <v>5</v>
+      </c>
+      <c r="S9" s="1">
+        <v>30</v>
+      </c>
+      <c r="T9" s="1">
+        <v>3</v>
+      </c>
+      <c r="U9" s="1">
+        <v>90</v>
+      </c>
+      <c r="V9" s="1">
+        <v>20</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="AA9" s="1">
         <v>10</v>
       </c>
-      <c r="S9" s="1">
-        <v>2</v>
-      </c>
-      <c r="T9" s="1">
-        <v>60</v>
-      </c>
-      <c r="U9" s="1">
-        <v>10</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="X9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="Z9" s="1">
+      <c r="AB9" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>35</v>
+      </c>
+      <c r="AE9" s="1">
         <v>3</v>
       </c>
-      <c r="AA9" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>6</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>15</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="1">
+      <c r="AF9" s="1">
         <v>5</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/EnemyEntityTable.xlsx
+++ b/AAAGameData/DataTables/EnemyEntityTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>IconId</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>敌人名称</t>
   </si>
   <si>
-    <t>图标ID</t>
-  </si>
-  <si>
     <t>描述</t>
   </si>
   <si>
@@ -258,6 +252,30 @@
   </si>
   <si>
     <t>Boss难度</t>
+  </si>
+  <si>
+    <t>黑化后羿-普通</t>
+  </si>
+  <si>
+    <t>黑化后羿-普通难度</t>
+  </si>
+  <si>
+    <t>黑化后羿-精英</t>
+  </si>
+  <si>
+    <t>黑化后羿-精英难度</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-普通</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-普通难度</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-精英</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-精英难度</t>
   </si>
 </sst>
 </file>
@@ -1229,42 +1247,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AE13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="34" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="32" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="17" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="24" width="23" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
-    <col min="26" max="26" width="28" customWidth="1"/>
-    <col min="27" max="27" width="32" customWidth="1"/>
-    <col min="28" max="28" width="22" customWidth="1"/>
-    <col min="29" max="29" width="12" customWidth="1"/>
-    <col min="30" max="30" width="32" customWidth="1"/>
-    <col min="31" max="31" width="20" customWidth="1"/>
-    <col min="32" max="32" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="23" width="23" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="28" customWidth="1"/>
+    <col min="26" max="26" width="32" customWidth="1"/>
+    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="20" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,9 +1317,8 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1394,672 +1410,1012 @@
       <c r="AE2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="1" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:31">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:32">
+    <row r="5" ht="15" customHeight="1" spans="1:31">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="1">
-        <v>11001</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="1">
+        <v>13010</v>
       </c>
       <c r="G5" s="1">
-        <v>1601</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="b">
+      <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L5" s="1">
-        <v>102</v>
+        <v>2601</v>
       </c>
       <c r="M5" s="1">
-        <v>2601</v>
+        <v>1</v>
       </c>
       <c r="N5" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O5" s="1">
+        <v>2</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="Q5" s="1">
         <v>8</v>
       </c>
-      <c r="P5" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0.35</v>
-      </c>
       <c r="R5" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S5" s="1">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="T5" s="1">
-        <v>1.5</v>
+        <v>60</v>
       </c>
       <c r="U5" s="1">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="V5" s="1">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="W5" s="1">
         <v>0.4</v>
       </c>
       <c r="X5" s="1">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" s="1">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="AA5" s="1">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="AB5" s="1">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="AC5" s="1">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="AD5" s="1">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AE5" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:32">
+    <row r="6" ht="15" customHeight="1" spans="1:31">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="1">
-        <v>11001</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="1">
+        <v>13011</v>
       </c>
       <c r="G6" s="1">
-        <v>1602</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="b">
+      <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1">
-        <v>101</v>
+        <v>2601</v>
       </c>
       <c r="M6" s="1">
-        <v>2601</v>
+        <v>2</v>
       </c>
       <c r="N6" s="1">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1">
+        <v>20</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T6" s="1">
+        <v>70</v>
+      </c>
+      <c r="U6" s="1">
+        <v>10</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1">
         <v>2</v>
       </c>
-      <c r="O6" s="1">
-        <v>10</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="R6" s="1">
-        <v>10</v>
-      </c>
-      <c r="S6" s="1">
-        <v>20</v>
-      </c>
-      <c r="T6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U6" s="1">
-        <v>70</v>
-      </c>
-      <c r="V6" s="1">
-        <v>10</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>1</v>
-      </c>
       <c r="Z6" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="1">
-        <v>7</v>
+        <v>0.35</v>
       </c>
       <c r="AB6" s="1">
-        <v>0.35</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" s="1">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="AD6" s="1">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AE6" s="1">
-        <v>8</v>
-      </c>
-      <c r="AF6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:32">
+    <row r="7" ht="15" customHeight="1" spans="1:31">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="1">
-        <v>11001</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="1">
+        <v>13010</v>
       </c>
       <c r="G7" s="1">
-        <v>1601</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
+      <c r="I7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>15</v>
       </c>
       <c r="K7" s="1">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="L7" s="1">
-        <v>101</v>
+        <v>2601</v>
       </c>
       <c r="M7" s="1">
-        <v>2601</v>
+        <v>3</v>
       </c>
       <c r="N7" s="1">
+        <v>12</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>6</v>
+      </c>
+      <c r="R7" s="1">
+        <v>16</v>
+      </c>
+      <c r="S7" s="1">
+        <v>2</v>
+      </c>
+      <c r="T7" s="1">
+        <v>70</v>
+      </c>
+      <c r="U7" s="1">
+        <v>8</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="X7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>22</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="1">
         <v>3</v>
       </c>
-      <c r="O7" s="1">
-        <v>12</v>
-      </c>
-      <c r="P7" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="R7" s="1">
-        <v>6</v>
-      </c>
-      <c r="S7" s="1">
-        <v>16</v>
-      </c>
-      <c r="T7" s="1">
-        <v>2</v>
-      </c>
-      <c r="U7" s="1">
-        <v>70</v>
-      </c>
-      <c r="V7" s="1">
-        <v>8</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>22</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF7" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:32">
+    <row r="8" ht="15" customHeight="1" spans="1:31">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="1">
-        <v>11001</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1">
+        <v>13011</v>
       </c>
       <c r="G8" s="1">
-        <v>1602</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
         <v>11</v>
       </c>
-      <c r="J8" s="1" t="b">
-        <v>1</v>
+      <c r="I8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>20</v>
       </c>
       <c r="K8" s="1">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="L8" s="1">
-        <v>102</v>
+        <v>2601</v>
       </c>
       <c r="M8" s="1">
-        <v>2601</v>
+        <v>4</v>
       </c>
       <c r="N8" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O8" s="1">
-        <v>15</v>
+        <v>2.2</v>
       </c>
       <c r="P8" s="1">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="R8" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="S8" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T8" s="1">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="U8" s="1">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="V8" s="1">
-        <v>14</v>
+        <v>0.35</v>
       </c>
       <c r="W8" s="1">
         <v>0.35</v>
       </c>
       <c r="X8" s="1">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="1">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" s="1">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>28</v>
+      </c>
+      <c r="AD8" s="1">
         <v>8</v>
       </c>
-      <c r="AB8" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>28</v>
-      </c>
       <c r="AE8" s="1">
-        <v>8</v>
-      </c>
-      <c r="AF8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:32">
+    <row r="9" ht="15" customHeight="1" spans="1:31">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="1">
+        <v>13012</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1">
+        <v>103</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M9" s="1">
+        <v>5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>20</v>
+      </c>
+      <c r="O9" s="1">
+        <v>3</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>5</v>
+      </c>
+      <c r="R9" s="1">
+        <v>30</v>
+      </c>
+      <c r="S9" s="1">
+        <v>3</v>
+      </c>
+      <c r="T9" s="1">
+        <v>90</v>
+      </c>
+      <c r="U9" s="1">
+        <v>20</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:31">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="1">
-        <v>11001</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="1">
-        <v>1603</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="F10" s="1">
+        <v>13001</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>102</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M10" s="1">
+        <v>6</v>
+      </c>
+      <c r="N10" s="1">
+        <v>8</v>
+      </c>
+      <c r="O10" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="P10" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>8</v>
+      </c>
+      <c r="R10" s="1">
         <v>12</v>
       </c>
-      <c r="J9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>30</v>
-      </c>
-      <c r="L9" s="1">
-        <v>103</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="S10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T10" s="1">
+        <v>60</v>
+      </c>
+      <c r="U10" s="1">
+        <v>6</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>18</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:31">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1">
+        <v>13001</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>15</v>
+      </c>
+      <c r="K11" s="1">
+        <v>101</v>
+      </c>
+      <c r="L11" s="1">
         <v>2601</v>
       </c>
-      <c r="N9" s="1">
-        <v>5</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="M11" s="1">
+        <v>7</v>
+      </c>
+      <c r="N11" s="1">
+        <v>12</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>6</v>
+      </c>
+      <c r="R11" s="1">
+        <v>16</v>
+      </c>
+      <c r="S11" s="1">
+        <v>2</v>
+      </c>
+      <c r="T11" s="1">
+        <v>70</v>
+      </c>
+      <c r="U11" s="1">
+        <v>8</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="X11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>22</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:31">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="1">
+        <v>13004</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>101</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M12" s="1">
+        <v>8</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>10</v>
+      </c>
+      <c r="R12" s="1">
         <v>20</v>
       </c>
-      <c r="P9" s="1">
+      <c r="S12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="1">
+        <v>70</v>
+      </c>
+      <c r="U12" s="1">
+        <v>10</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>7</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>25</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:31">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="1">
+        <v>13004</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>20</v>
+      </c>
+      <c r="K13" s="1">
+        <v>102</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2601</v>
+      </c>
+      <c r="M13" s="1">
+        <v>9</v>
+      </c>
+      <c r="N13" s="1">
+        <v>15</v>
+      </c>
+      <c r="O13" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>8</v>
+      </c>
+      <c r="R13" s="1">
+        <v>25</v>
+      </c>
+      <c r="S13" s="1">
+        <v>2</v>
+      </c>
+      <c r="T13" s="1">
+        <v>80</v>
+      </c>
+      <c r="U13" s="1">
+        <v>14</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="X13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>28</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>8</v>
+      </c>
+      <c r="AE13" s="1">
         <v>3</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="R9" s="1">
-        <v>5</v>
-      </c>
-      <c r="S9" s="1">
-        <v>30</v>
-      </c>
-      <c r="T9" s="1">
-        <v>3</v>
-      </c>
-      <c r="U9" s="1">
-        <v>90</v>
-      </c>
-      <c r="V9" s="1">
-        <v>20</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="X9" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>10</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>35</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
